--- a/artfynd/A 43363-2026 artfynd.xlsx
+++ b/artfynd/A 43363-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008095</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137008097</v>
       </c>
       <c r="B3" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137008096</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43363-2026 artfynd.xlsx
+++ b/artfynd/A 43363-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008095</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137008097</v>
       </c>
       <c r="B3" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137008096</v>
       </c>
       <c r="B4" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43363-2026 artfynd.xlsx
+++ b/artfynd/A 43363-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008095</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137008097</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137008096</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43363-2026 artfynd.xlsx
+++ b/artfynd/A 43363-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008095</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137008097</v>
       </c>
       <c r="B3" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137008096</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43363-2026 artfynd.xlsx
+++ b/artfynd/A 43363-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008095</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137008097</v>
       </c>
       <c r="B3" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137008096</v>
       </c>
       <c r="B4" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43363-2026 artfynd.xlsx
+++ b/artfynd/A 43363-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008095</v>
       </c>
       <c r="B2" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137008097</v>
       </c>
       <c r="B3" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137008096</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43363-2026 artfynd.xlsx
+++ b/artfynd/A 43363-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008095</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137008097</v>
       </c>
       <c r="B3" t="n">
-        <v>92206</v>
+        <v>92207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137008096</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43363-2026 artfynd.xlsx
+++ b/artfynd/A 43363-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008095</v>
       </c>
       <c r="B2" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137008097</v>
       </c>
       <c r="B3" t="n">
-        <v>92207</v>
+        <v>92210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137008096</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
